--- a/site/ValueSet-vs-via-administracion.xlsx
+++ b/site/ValueSet-vs-via-administracion.xlsx
@@ -8,13 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>Property</t>
   </si>
@@ -58,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T15:20:04-03:00</t>
+    <t>2026-10-06T01:23:13-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -67,6 +66,12 @@
     <t>AGESIC</t>
   </si>
   <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>AGESIC (https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/salud-digital)</t>
+  </si>
+  <si>
     <t>Jurisdiction</t>
   </si>
   <si>
@@ -104,15 +109,6 @@
   </si>
   <si>
     <t>http://terminology.hl7.org/CodeSystem/v3-RouteOfAdministration</t>
-  </si>
-  <si>
-    <t>urn:hl7-org:sdwg:ccda-nonXMLBody:2.1</t>
-  </si>
-  <si>
-    <t>C-CDA 2.1 con cuerpo no estructurado</t>
-  </si>
-  <si>
-    <t>http://ihe.net/fhir/ihe.formatcode.fhir/CodeSystem/formatcode</t>
   </si>
 </sst>
 </file>
@@ -246,7 +242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -343,20 +339,28 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>24</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -375,80 +379,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s" s="2">
         <v>31</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/site/ValueSet-vs-via-administracion.xlsx
+++ b/site/ValueSet-vs-via-administracion.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T01:23:13-03:00</t>
+    <t>2026-10-28T18:02:56-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
